--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1172,6 +1172,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1181,7 +1184,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1510,6 +1513,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1553,7 +1559,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1883,6 +1889,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1892,7 +1901,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2221,6 +2230,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2264,7 +2276,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2594,6 +2606,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2603,7 +2618,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2932,6 +2947,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2954,11 +2972,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="473501696"/>
-        <c:axId val="479633408"/>
+        <c:axId val="492253568"/>
+        <c:axId val="492255104"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="473501696"/>
+        <c:axId val="492253568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3001,14 +3019,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479633408"/>
+        <c:crossAx val="492255104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479633408"/>
+        <c:axId val="492255104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3057,7 +3075,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="473501696"/>
+        <c:crossAx val="492253568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3242,7 +3260,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3572,6 +3590,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3581,7 +3602,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3910,6 +3931,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3953,7 +3977,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4283,6 +4307,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4292,7 +4319,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4621,6 +4648,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4664,7 +4694,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4994,6 +5024,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5003,7 +5036,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5332,6 +5365,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5354,11 +5390,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="480035968"/>
-        <c:axId val="480037504"/>
+        <c:axId val="492295680"/>
+        <c:axId val="492297216"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="480035968"/>
+        <c:axId val="492295680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5401,14 +5437,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480037504"/>
+        <c:crossAx val="492297216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="480037504"/>
+        <c:axId val="492297216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5457,7 +5493,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480035968"/>
+        <c:crossAx val="492295680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5642,7 +5678,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5972,6 +6008,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5981,7 +6020,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6310,6 +6349,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6353,7 +6395,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6683,6 +6725,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6692,7 +6737,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7021,6 +7066,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7064,7 +7112,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7394,6 +7442,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7403,7 +7454,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7732,6 +7783,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7754,11 +7808,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="524069888"/>
-        <c:axId val="559989504"/>
+        <c:axId val="492493440"/>
+        <c:axId val="492499328"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="524069888"/>
+        <c:axId val="492493440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7801,14 +7855,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559989504"/>
+        <c:crossAx val="492499328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="559989504"/>
+        <c:axId val="492499328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7857,7 +7911,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524069888"/>
+        <c:crossAx val="492493440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8042,7 +8096,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8372,6 +8426,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8381,7 +8438,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8710,6 +8767,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8753,7 +8813,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9083,6 +9143,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9092,7 +9155,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9421,6 +9484,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9464,7 +9530,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9794,6 +9860,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9803,7 +9872,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10132,6 +10201,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10154,11 +10226,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="614938880"/>
-        <c:axId val="458747904"/>
+        <c:axId val="495562752"/>
+        <c:axId val="495564288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="614938880"/>
+        <c:axId val="495562752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10201,14 +10273,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="458747904"/>
+        <c:crossAx val="495564288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="458747904"/>
+        <c:axId val="495564288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10257,7 +10329,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614938880"/>
+        <c:crossAx val="495562752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10442,7 +10514,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10772,6 +10844,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10781,7 +10856,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11110,6 +11185,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11153,7 +11231,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11483,6 +11561,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11492,7 +11573,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11821,6 +11902,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11864,7 +11948,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12194,6 +12278,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12203,7 +12290,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12532,6 +12619,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12554,11 +12644,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465579392"/>
-        <c:axId val="465581184"/>
+        <c:axId val="510221696"/>
+        <c:axId val="510223488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465579392"/>
+        <c:axId val="510221696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12601,14 +12691,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465581184"/>
+        <c:crossAx val="510223488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465581184"/>
+        <c:axId val="510223488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12657,7 +12747,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465579392"/>
+        <c:crossAx val="510221696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12842,7 +12932,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13172,6 +13262,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13181,7 +13274,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13510,6 +13603,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13553,7 +13649,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13883,6 +13979,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13892,7 +13991,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14221,6 +14320,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14264,7 +14366,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14594,6 +14696,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14603,7 +14708,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14932,6 +15037,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -14954,11 +15062,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="465625856"/>
-        <c:axId val="465627392"/>
+        <c:axId val="510599936"/>
+        <c:axId val="510601472"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="465625856"/>
+        <c:axId val="510599936"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15001,14 +15109,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465627392"/>
+        <c:crossAx val="510601472"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465627392"/>
+        <c:axId val="510601472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15057,7 +15165,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465625856"/>
+        <c:crossAx val="510599936"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15242,7 +15350,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15572,6 +15680,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15581,7 +15692,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15910,6 +16021,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -15953,7 +16067,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16283,6 +16397,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16292,7 +16409,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16621,6 +16738,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16664,7 +16784,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16994,6 +17114,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17003,7 +17126,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17332,6 +17455,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17354,11 +17480,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467019648"/>
-        <c:axId val="467021184"/>
+        <c:axId val="511133952"/>
+        <c:axId val="511135744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467019648"/>
+        <c:axId val="511133952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17401,14 +17527,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467021184"/>
+        <c:crossAx val="511135744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467021184"/>
+        <c:axId val="511135744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17457,7 +17583,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467019648"/>
+        <c:crossAx val="511133952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17642,7 +17768,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17972,6 +18098,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17981,7 +18110,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18310,6 +18439,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18353,7 +18485,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18683,6 +18815,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18692,7 +18827,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19021,6 +19156,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19064,7 +19202,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19394,6 +19532,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19403,7 +19544,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19732,6 +19873,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19754,11 +19898,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467074048"/>
-        <c:axId val="479658752"/>
+        <c:axId val="511454592"/>
+        <c:axId val="511480960"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467074048"/>
+        <c:axId val="511454592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19801,14 +19945,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479658752"/>
+        <c:crossAx val="511480960"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="479658752"/>
+        <c:axId val="511480960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19857,7 +20001,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467074048"/>
+        <c:crossAx val="511454592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20579,7 +20723,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25227,6 +25371,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I114" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J114" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K114" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25245,7 +25424,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31221,6 +31400,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="114" spans="1:15" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I114" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J114" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K114" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L114" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M114" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N114" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O114" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -31239,7 +31465,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37506,6 +37732,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="114" spans="1:16" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I114" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J114" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K114" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L114" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M114" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N114" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O114" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -37524,7 +37800,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -42847,6 +43123,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="114" spans="1:13" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="20">
+        <v>1519418</v>
+      </c>
+      <c r="E114" s="20">
+        <v>1843565.8817559057</v>
+      </c>
+      <c r="F114" s="21">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>0</v>
+      </c>
+      <c r="I114" s="22">
+        <v>0</v>
+      </c>
+      <c r="J114" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K114" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L114" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M114" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -42865,7 +43182,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -47513,6 +47830,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I114" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J114" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K114" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -47531,7 +47883,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -53507,6 +53859,53 @@
         <v>0.2</v>
       </c>
     </row>
+    <row r="114" spans="1:15" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="21">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I114" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J114" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K114" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L114" s="26">
+        <v>0.19018078074406178</v>
+      </c>
+      <c r="M114" s="27">
+        <v>0.25423220629573501</v>
+      </c>
+      <c r="N114" s="27">
+        <v>74.805935689687729</v>
+      </c>
+      <c r="O114" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -53525,7 +53924,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -59791,6 +60190,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="114" spans="1:16" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I114" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J114" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K114" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L114" s="26">
+        <v>86.321154877675269</v>
+      </c>
+      <c r="M114" s="27">
+        <v>81.396334035405502</v>
+      </c>
+      <c r="N114" s="27">
+        <v>77.031747408613512</v>
+      </c>
+      <c r="O114" s="27">
+        <v>90.125507288989468</v>
+      </c>
+      <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -59809,7 +60258,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH113"/>
+  <dimension ref="A1:AH114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -65132,6 +65581,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="114" spans="1:13" ht="12.75">
+      <c r="A114" s="15">
+        <v>46203</v>
+      </c>
+      <c r="B114" s="25">
+        <v>3.4470000267028809</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.3554563352387954</v>
+      </c>
+      <c r="D114" s="20">
+        <v>1519418</v>
+      </c>
+      <c r="E114" s="20">
+        <v>1843565.8817559057</v>
+      </c>
+      <c r="F114" s="21">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>0</v>
+      </c>
+      <c r="I114" s="22">
+        <v>0</v>
+      </c>
+      <c r="J114" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K114" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L114" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M114" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1175,6 +1175,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1184,7 +1187,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1516,6 +1519,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1559,7 +1565,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1892,6 +1898,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1901,7 +1910,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2233,6 +2242,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2276,7 +2288,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2609,6 +2621,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2618,7 +2633,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2950,6 +2965,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2972,11 +2990,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="492253568"/>
-        <c:axId val="492255104"/>
+        <c:axId val="373774592"/>
+        <c:axId val="373788672"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="492253568"/>
+        <c:axId val="373774592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3019,14 +3037,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492255104"/>
+        <c:crossAx val="373788672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492255104"/>
+        <c:axId val="373788672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3075,7 +3093,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492253568"/>
+        <c:crossAx val="373774592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3260,7 +3278,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3593,6 +3611,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3602,7 +3623,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3934,6 +3955,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -3977,7 +4001,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4310,6 +4334,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4319,7 +4346,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4651,6 +4678,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4694,7 +4724,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5027,6 +5057,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5036,7 +5069,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5368,6 +5401,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5390,11 +5426,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="492295680"/>
-        <c:axId val="492297216"/>
+        <c:axId val="373812608"/>
+        <c:axId val="494408832"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="492295680"/>
+        <c:axId val="373812608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5437,14 +5473,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492297216"/>
+        <c:crossAx val="494408832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492297216"/>
+        <c:axId val="494408832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5493,7 +5529,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492295680"/>
+        <c:crossAx val="373812608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5678,7 +5714,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6011,6 +6047,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6020,7 +6059,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6352,6 +6391,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6395,7 +6437,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6728,6 +6770,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6737,7 +6782,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7069,6 +7114,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7112,7 +7160,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7445,6 +7493,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7454,7 +7505,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7786,6 +7837,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7808,11 +7862,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="492493440"/>
-        <c:axId val="492499328"/>
+        <c:axId val="494465792"/>
+        <c:axId val="494467328"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="492493440"/>
+        <c:axId val="494465792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7855,14 +7909,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492499328"/>
+        <c:crossAx val="494467328"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="492499328"/>
+        <c:axId val="494467328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7911,7 +7965,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="492493440"/>
+        <c:crossAx val="494465792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8096,7 +8150,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8429,6 +8483,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8438,7 +8495,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8770,6 +8827,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8813,7 +8873,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9146,6 +9206,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9155,7 +9218,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9487,6 +9550,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9530,7 +9596,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9863,6 +9929,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9872,7 +9941,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10204,6 +10273,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10226,11 +10298,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="495562752"/>
-        <c:axId val="495564288"/>
+        <c:axId val="494565248"/>
+        <c:axId val="494566784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="495562752"/>
+        <c:axId val="494565248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10273,14 +10345,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495564288"/>
+        <c:crossAx val="494566784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="495564288"/>
+        <c:axId val="494566784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10329,7 +10401,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495562752"/>
+        <c:crossAx val="494565248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10514,7 +10586,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10847,6 +10919,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10856,7 +10931,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11188,6 +11263,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11231,7 +11309,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11564,6 +11642,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11573,7 +11654,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11905,6 +11986,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -11948,7 +12032,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12281,6 +12365,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12290,7 +12377,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12622,6 +12709,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12644,11 +12734,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510221696"/>
-        <c:axId val="510223488"/>
+        <c:axId val="523873280"/>
+        <c:axId val="523875072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510221696"/>
+        <c:axId val="523873280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12691,14 +12781,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510223488"/>
+        <c:crossAx val="523875072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510223488"/>
+        <c:axId val="523875072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12747,7 +12837,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510221696"/>
+        <c:crossAx val="523873280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12932,7 +13022,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13265,6 +13355,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13274,7 +13367,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13606,6 +13699,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13649,7 +13745,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13982,6 +14078,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13991,7 +14090,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14323,6 +14422,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14366,7 +14468,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14699,6 +14801,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14708,7 +14813,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15040,6 +15145,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -15062,11 +15170,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510599936"/>
-        <c:axId val="510601472"/>
+        <c:axId val="531014016"/>
+        <c:axId val="531015552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510599936"/>
+        <c:axId val="531014016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15109,14 +15217,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510601472"/>
+        <c:crossAx val="531015552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="510601472"/>
+        <c:axId val="531015552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15165,7 +15273,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510599936"/>
+        <c:crossAx val="531014016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15350,7 +15458,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15683,6 +15791,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15692,7 +15803,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16024,6 +16135,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -16067,7 +16181,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16400,6 +16514,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16409,7 +16526,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16741,6 +16858,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16784,7 +16904,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17117,6 +17237,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17126,7 +17249,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17458,6 +17581,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17480,11 +17606,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511133952"/>
-        <c:axId val="511135744"/>
+        <c:axId val="547694080"/>
+        <c:axId val="547695616"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511133952"/>
+        <c:axId val="547694080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17527,14 +17653,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511135744"/>
+        <c:crossAx val="547695616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511135744"/>
+        <c:axId val="547695616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17583,7 +17709,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511133952"/>
+        <c:crossAx val="547694080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17768,7 +17894,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18101,6 +18227,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18110,7 +18239,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18442,6 +18571,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18485,7 +18617,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18818,6 +18950,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18827,7 +18962,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19159,6 +19294,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19202,7 +19340,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19535,6 +19673,9 @@
                 </c:pt>
                 <c:pt idx="110">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19544,7 +19685,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="111"/>
+                <c:ptCount val="112"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19876,6 +20017,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="110">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="111">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -19898,11 +20042,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="511454592"/>
-        <c:axId val="511480960"/>
+        <c:axId val="547949184"/>
+        <c:axId val="547967360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="511454592"/>
+        <c:axId val="547949184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -19945,14 +20089,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511480960"/>
+        <c:crossAx val="547967360"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="511480960"/>
+        <c:axId val="547967360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20001,7 +20145,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="511454592"/>
+        <c:crossAx val="547949184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20723,7 +20867,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25406,6 +25550,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J115" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25424,7 +25603,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31435,16 +31614,63 @@
         <v>1938.211964032281</v>
       </c>
       <c r="L114" s="26">
-        <v>0.19018078074406178</v>
+        <v>0.22298399794060811</v>
       </c>
       <c r="M114" s="27">
-        <v>0.25423220629573501</v>
+        <v>0.27636018590033579</v>
       </c>
       <c r="N114" s="27">
-        <v>74.805935689687729</v>
+        <v>80.686006638099158</v>
       </c>
       <c r="O114" s="27">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J115" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L115" s="26">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="M115" s="27">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N115" s="27">
+        <v>55.036007935137903</v>
+      </c>
+      <c r="O115" s="27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -31465,7 +31691,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -37767,18 +37993,68 @@
         <v>1152.2841821809159</v>
       </c>
       <c r="L114" s="26">
-        <v>86.321154877675269</v>
+        <v>99.924817475329945</v>
       </c>
       <c r="M114" s="27">
-        <v>81.396334035405502</v>
+        <v>87.572495182046978</v>
       </c>
       <c r="N114" s="27">
-        <v>77.031747408613512</v>
+        <v>80.545329999757996</v>
       </c>
       <c r="O114" s="27">
-        <v>90.125507288989468</v>
+        <v>101.62682554662496</v>
       </c>
       <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I115" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J115" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K115" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L115" s="26">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="M115" s="27">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="N115" s="27">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="O115" s="27">
+        <v>66.349664726624525</v>
+      </c>
+      <c r="P115" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -37800,7 +38076,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -43164,6 +43440,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="115" spans="1:13" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="20">
+        <v>842345</v>
+      </c>
+      <c r="E115" s="20">
+        <v>1833164.83510292</v>
+      </c>
+      <c r="F115" s="21">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>0</v>
+      </c>
+      <c r="I115" s="22">
+        <v>0</v>
+      </c>
+      <c r="J115" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K115" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L115" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M115" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -43182,7 +43499,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF114"/>
+  <dimension ref="A1:AF115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -47865,6 +48182,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="115" spans="1:11" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I115" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J115" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K115" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -47883,7 +48235,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -53894,16 +54246,63 @@
         <v>425.75844436164391</v>
       </c>
       <c r="L114" s="26">
-        <v>0.19018078074406178</v>
+        <v>0.22298399794060811</v>
       </c>
       <c r="M114" s="27">
-        <v>0.25423220629573501</v>
+        <v>0.27636018590033579</v>
       </c>
       <c r="N114" s="27">
-        <v>74.805935689687729</v>
+        <v>80.686006638099158</v>
       </c>
       <c r="O114" s="27">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="21">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I115" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J115" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K115" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L115" s="26">
+        <v>0.1858199982838401</v>
+      </c>
+      <c r="M115" s="27">
+        <v>0.33763349715124008</v>
+      </c>
+      <c r="N115" s="27">
+        <v>55.036007935137903</v>
+      </c>
+      <c r="O115" s="27">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -53924,7 +54323,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -60225,18 +60624,68 @@
         <v>242.17499191669597</v>
       </c>
       <c r="L114" s="26">
-        <v>86.321154877675269</v>
+        <v>99.924817475329945</v>
       </c>
       <c r="M114" s="27">
-        <v>81.396334035405502</v>
+        <v>87.572495182046978</v>
       </c>
       <c r="N114" s="27">
-        <v>77.031747408613512</v>
+        <v>80.545329999757996</v>
       </c>
       <c r="O114" s="27">
-        <v>90.125507288989468</v>
+        <v>101.62682554662496</v>
       </c>
       <c r="P114" s="27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="21">
+        <v>0</v>
+      </c>
+      <c r="E115" s="22">
+        <v>0</v>
+      </c>
+      <c r="F115" s="22">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I115" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J115" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K115" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L115" s="26">
+        <v>48.239429998294135</v>
+      </c>
+      <c r="M115" s="27">
+        <v>74.461473454129361</v>
+      </c>
+      <c r="N115" s="27">
+        <v>78.51737781788178</v>
+      </c>
+      <c r="O115" s="27">
+        <v>66.349664726624525</v>
+      </c>
+      <c r="P115" s="27">
         <v>0.95</v>
       </c>
     </row>
@@ -60258,7 +60707,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH114"/>
+  <dimension ref="A1:AH115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -65622,6 +66071,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="115" spans="1:13" ht="12.75">
+      <c r="A115" s="15">
+        <v>46234</v>
+      </c>
+      <c r="B115" s="25">
+        <v>2.8029999732971191</v>
+      </c>
+      <c r="C115" s="20">
+        <v>1.373083331676451</v>
+      </c>
+      <c r="D115" s="20">
+        <v>842345</v>
+      </c>
+      <c r="E115" s="20">
+        <v>1833164.83510292</v>
+      </c>
+      <c r="F115" s="21">
+        <v>0</v>
+      </c>
+      <c r="G115" s="22">
+        <v>0</v>
+      </c>
+      <c r="H115" s="22">
+        <v>0</v>
+      </c>
+      <c r="I115" s="22">
+        <v>0</v>
+      </c>
+      <c r="J115" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K115" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L115" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M115" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">

--- a/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
+++ b/lai/valuationquan/AILOF/csiAILOFmodel4mean.xlsx
@@ -842,7 +842,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1178,6 +1178,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1187,7 +1190,7 @@
               <c:f>'model4(1)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1522,6 +1525,9 @@
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>782.67846849814737</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>782.67846849814737</c:v>
                 </c:pt>
               </c:numCache>
@@ -1565,7 +1571,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -1901,6 +1907,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1910,7 +1919,7 @@
               <c:f>'model4(1)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2245,6 +2254,9 @@
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1240.6008762862457</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1240.6008762862457</c:v>
                 </c:pt>
               </c:numCache>
@@ -2288,7 +2300,7 @@
               <c:f>'model4(1)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -2624,6 +2636,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2633,7 +2648,7 @@
               <c:f>'model4(1)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2968,6 +2983,9 @@
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>457.92240778809833</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>457.92240778809833</c:v>
                 </c:pt>
               </c:numCache>
@@ -2990,11 +3008,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="373774592"/>
-        <c:axId val="373788672"/>
+        <c:axId val="485510144"/>
+        <c:axId val="489280256"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="373774592"/>
+        <c:axId val="485510144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3037,14 +3055,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373788672"/>
+        <c:crossAx val="489280256"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="373788672"/>
+        <c:axId val="489280256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3093,7 +3111,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373774592"/>
+        <c:crossAx val="485510144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3278,7 +3296,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -3614,6 +3632,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3623,7 +3644,7 @@
               <c:f>'model4(1)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3958,6 +3979,9 @@
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1081.9760781597654</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1081.9760781597654</c:v>
                 </c:pt>
               </c:numCache>
@@ -4001,7 +4025,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -4337,6 +4361,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4346,7 +4373,7 @@
               <c:f>'model4(1)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4681,6 +4708,9 @@
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1938.211964032281</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1938.211964032281</c:v>
                 </c:pt>
               </c:numCache>
@@ -4724,7 +4754,7 @@
               <c:f>'model4(1)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -5060,6 +5090,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5069,7 +5102,7 @@
               <c:f>'model4(1)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5404,6 +5437,9 @@
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>856.23588587251561</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>856.23588587251561</c:v>
                 </c:pt>
               </c:numCache>
@@ -5426,11 +5462,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="373812608"/>
-        <c:axId val="494408832"/>
+        <c:axId val="397455360"/>
+        <c:axId val="397456896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="373812608"/>
+        <c:axId val="397455360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5473,14 +5509,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494408832"/>
+        <c:crossAx val="397456896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494408832"/>
+        <c:axId val="397456896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5529,7 +5565,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="373812608"/>
+        <c:crossAx val="397455360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5714,7 +5750,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6050,6 +6086,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6059,7 +6098,7 @@
               <c:f>'model4(1)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6394,6 +6433,9 @@
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>717.1927699657906</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>717.1927699657906</c:v>
                 </c:pt>
               </c:numCache>
@@ -6437,7 +6479,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -6773,6 +6815,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6782,7 +6827,7 @@
               <c:f>'model4(1)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7117,6 +7162,9 @@
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>1152.2841821809159</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>1152.2841821809159</c:v>
                 </c:pt>
               </c:numCache>
@@ -7160,7 +7208,7 @@
               <c:f>'model4(1)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -7496,6 +7544,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7505,7 +7556,7 @@
               <c:f>'model4(1)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7840,6 +7891,9 @@
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>435.09141221512527</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>435.09141221512527</c:v>
                 </c:pt>
               </c:numCache>
@@ -7862,11 +7916,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494465792"/>
-        <c:axId val="494467328"/>
+        <c:axId val="413791360"/>
+        <c:axId val="413792896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494465792"/>
+        <c:axId val="413791360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7909,14 +7963,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494467328"/>
+        <c:crossAx val="413792896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494467328"/>
+        <c:axId val="413792896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7965,7 +8019,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494465792"/>
+        <c:crossAx val="413791360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8150,7 +8204,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -8486,6 +8540,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8495,7 +8552,7 @@
               <c:f>'model4(1)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8830,6 +8887,9 @@
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>366.42697665235454</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>366.42697665235454</c:v>
                 </c:pt>
               </c:numCache>
@@ -8873,7 +8933,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9209,6 +9269,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9218,7 +9281,7 @@
               <c:f>'model4(1)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -9553,6 +9616,9 @@
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>579.4237932103814</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>579.4237932103814</c:v>
                 </c:pt>
               </c:numCache>
@@ -9596,7 +9662,7 @@
               <c:f>'model4(1)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -9932,6 +9998,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9941,7 +10010,7 @@
               <c:f>'model4(1)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -10276,6 +10345,9 @@
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>212.99681655802686</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>212.99681655802686</c:v>
                 </c:pt>
               </c:numCache>
@@ -10298,11 +10370,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="494565248"/>
-        <c:axId val="494566784"/>
+        <c:axId val="417827072"/>
+        <c:axId val="417837056"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="494565248"/>
+        <c:axId val="417827072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10345,14 +10417,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494566784"/>
+        <c:crossAx val="417837056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494566784"/>
+        <c:axId val="417837056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10401,7 +10473,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494565248"/>
+        <c:crossAx val="417827072"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10586,7 +10658,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -10922,6 +10994,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10931,7 +11006,7 @@
               <c:f>'model4(3)'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11266,6 +11341,9 @@
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>155.51321719002138</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>155.51321719002138</c:v>
                 </c:pt>
               </c:numCache>
@@ -11309,7 +11387,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -11645,6 +11723,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11654,7 +11735,7 @@
               <c:f>'model4(3)'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11989,6 +12070,9 @@
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>260.7091440429981</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>260.7091440429981</c:v>
                 </c:pt>
               </c:numCache>
@@ -12032,7 +12116,7 @@
               <c:f>'model4(3)'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -12368,6 +12452,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12377,7 +12464,7 @@
               <c:f>'model4(3)'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -12712,6 +12799,9 @@
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>105.19592685297673</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>105.19592685297673</c:v>
                 </c:pt>
               </c:numCache>
@@ -12734,11 +12824,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523873280"/>
-        <c:axId val="523875072"/>
+        <c:axId val="417951104"/>
+        <c:axId val="417961088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523873280"/>
+        <c:axId val="417951104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12781,14 +12871,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523875072"/>
+        <c:crossAx val="417961088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523875072"/>
+        <c:axId val="417961088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12837,7 +12927,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523873280"/>
+        <c:crossAx val="417951104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13022,7 +13112,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -13358,6 +13448,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13367,7 +13460,7 @@
               <c:f>'model4(3)&amp;RSI'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -13702,6 +13795,9 @@
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>228.82879320428773</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>228.82879320428773</c:v>
                 </c:pt>
               </c:numCache>
@@ -13745,7 +13841,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14081,6 +14177,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14090,7 +14189,7 @@
               <c:f>'model4(3)&amp;RSI'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -14425,6 +14524,9 @@
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>425.75844436164391</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>425.75844436164391</c:v>
                 </c:pt>
               </c:numCache>
@@ -14468,7 +14570,7 @@
               <c:f>'model4(3)&amp;RSI'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -14804,6 +14906,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14813,7 +14918,7 @@
               <c:f>'model4(3)&amp;RSI'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -15148,6 +15253,9 @@
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>196.92965115735618</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>196.92965115735618</c:v>
                 </c:pt>
               </c:numCache>
@@ -15170,11 +15278,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="531014016"/>
-        <c:axId val="531015552"/>
+        <c:axId val="418042624"/>
+        <c:axId val="418044160"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="531014016"/>
+        <c:axId val="418042624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15217,14 +15325,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531015552"/>
+        <c:crossAx val="418044160"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="531015552"/>
+        <c:axId val="418044160"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -15273,7 +15381,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="531014016"/>
+        <c:crossAx val="418042624"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -15458,7 +15566,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -15794,6 +15902,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15803,7 +15914,7 @@
               <c:f>'model4(3)&amp;KDJ'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16138,6 +16249,9 @@
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>143.77000931573409</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>143.77000931573409</c:v>
                 </c:pt>
               </c:numCache>
@@ -16181,7 +16295,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -16517,6 +16631,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16526,7 +16643,7 @@
               <c:f>'model4(3)&amp;KDJ'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -16861,6 +16978,9 @@
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>242.17499191669597</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>242.17499191669597</c:v>
                 </c:pt>
               </c:numCache>
@@ -16904,7 +17024,7 @@
               <c:f>'model4(3)&amp;KDJ'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -17240,6 +17360,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -17249,7 +17372,7 @@
               <c:f>'model4(3)&amp;KDJ'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -17584,6 +17707,9 @@
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>98.404982600961887</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>98.404982600961887</c:v>
                 </c:pt>
               </c:numCache>
@@ -17606,11 +17732,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547694080"/>
-        <c:axId val="547695616"/>
+        <c:axId val="422950784"/>
+        <c:axId val="422952320"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547694080"/>
+        <c:axId val="422950784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17653,14 +17779,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547695616"/>
+        <c:crossAx val="422952320"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547695616"/>
+        <c:axId val="422952320"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -17709,7 +17835,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547694080"/>
+        <c:crossAx val="422950784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -17894,7 +18020,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18230,6 +18356,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18239,7 +18368,7 @@
               <c:f>'model4(3)vol'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -18574,6 +18703,9 @@
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>75.378225802571194</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>75.378225802571194</c:v>
                 </c:pt>
               </c:numCache>
@@ -18617,7 +18749,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -18953,6 +19085,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -18962,7 +19097,7 @@
               <c:f>'model4(3)vol'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -19297,6 +19432,9 @@
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>125.02031660046136</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>125.02031660046136</c:v>
                 </c:pt>
               </c:numCache>
@@ -19340,7 +19478,7 @@
               <c:f>'model4(3)vol'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>42853</c:v>
                 </c:pt>
@@ -19676,6 +19814,9 @@
                 </c:pt>
                 <c:pt idx="111">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -19685,7 +19826,7 @@
               <c:f>'model4(3)vol'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="112"/>
+                <c:ptCount val="113"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -20020,6 +20161,9 @@
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
                 <c:pt idx="111">
+                  <c:v>49.642090797890162</c:v>
+                </c:pt>
+                <c:pt idx="112">
                   <c:v>49.642090797890162</c:v>
                 </c:pt>
               </c:numCache>
@@ -20042,11 +20186,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="547949184"/>
-        <c:axId val="547967360"/>
+        <c:axId val="442334208"/>
+        <c:axId val="442348288"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="547949184"/>
+        <c:axId val="442334208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20089,14 +20233,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547967360"/>
+        <c:crossAx val="442348288"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="547967360"/>
+        <c:axId val="442348288"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -20145,7 +20289,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="547949184"/>
+        <c:crossAx val="442334208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -20867,7 +21011,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -25585,6 +25729,41 @@
         <v>1240.6008762862457</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>782.67846849814737</v>
+      </c>
+      <c r="I116" s="22">
+        <v>1240.6008762862457</v>
+      </c>
+      <c r="J116" s="22">
+        <v>457.92240778809833</v>
+      </c>
+      <c r="K116" s="21">
+        <v>1240.6008762862457</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -25603,7 +25782,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -31673,6 +31852,53 @@
         <v>1</v>
       </c>
     </row>
+    <row r="116" spans="1:15" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>1081.9760781597654</v>
+      </c>
+      <c r="I116" s="22">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="J116" s="22">
+        <v>856.23588587251561</v>
+      </c>
+      <c r="K116" s="21">
+        <v>1938.211964032281</v>
+      </c>
+      <c r="L116" s="26">
+        <v>0.15551665665346456</v>
+      </c>
+      <c r="M116" s="27">
+        <v>0.28202790570963121</v>
+      </c>
+      <c r="N116" s="27">
+        <v>55.142293902497926</v>
+      </c>
+      <c r="O116" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -31691,7 +31917,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -38058,6 +38284,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="116" spans="1:16" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>717.1927699657906</v>
+      </c>
+      <c r="I116" s="22">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="J116" s="22">
+        <v>435.09141221512527</v>
+      </c>
+      <c r="K116" s="21">
+        <v>1152.2841821809159</v>
+      </c>
+      <c r="L116" s="26">
+        <v>44.283524022760979</v>
+      </c>
+      <c r="M116" s="27">
+        <v>64.40215697700657</v>
+      </c>
+      <c r="N116" s="27">
+        <v>73.812304204256705</v>
+      </c>
+      <c r="O116" s="27">
+        <v>45.581862522506299</v>
+      </c>
+      <c r="P116" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -38076,7 +38352,7 @@
   <sheetPr codeName="Sheet4">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -43481,6 +43757,47 @@
         <v>579.4237932103814</v>
       </c>
     </row>
+    <row r="116" spans="1:13" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="20">
+        <v>934559.9375</v>
+      </c>
+      <c r="E116" s="20">
+        <v>1822584.096999204</v>
+      </c>
+      <c r="F116" s="21">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>0</v>
+      </c>
+      <c r="I116" s="22">
+        <v>0</v>
+      </c>
+      <c r="J116" s="22">
+        <v>366.42697665235454</v>
+      </c>
+      <c r="K116" s="22">
+        <v>579.4237932103814</v>
+      </c>
+      <c r="L116" s="22">
+        <v>212.99681655802686</v>
+      </c>
+      <c r="M116" s="21">
+        <v>579.4237932103814</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
@@ -43499,7 +43816,7 @@
   <sheetPr codeName="Sheet5">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF115"/>
+  <dimension ref="A1:AF116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -48217,6 +48534,41 @@
         <v>260.7091440429981</v>
       </c>
     </row>
+    <row r="116" spans="1:11" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>155.51321719002138</v>
+      </c>
+      <c r="I116" s="22">
+        <v>260.7091440429981</v>
+      </c>
+      <c r="J116" s="22">
+        <v>105.19592685297673</v>
+      </c>
+      <c r="K116" s="21">
+        <v>260.7091440429981</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -48235,7 +48587,7 @@
   <sheetPr codeName="Sheet6">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -54305,6 +54657,53 @@
         <v>1</v>
       </c>
     </row>
+    <row r="116" spans="1:15" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="21">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>228.82879320428773</v>
+      </c>
+      <c r="I116" s="22">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="J116" s="22">
+        <v>196.92965115735618</v>
+      </c>
+      <c r="K116" s="21">
+        <v>425.75844436164391</v>
+      </c>
+      <c r="L116" s="26">
+        <v>0.15551665665346456</v>
+      </c>
+      <c r="M116" s="27">
+        <v>0.28202790570963121</v>
+      </c>
+      <c r="N116" s="27">
+        <v>55.142293902497926</v>
+      </c>
+      <c r="O116" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -54323,7 +54722,7 @@
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -60689,6 +61088,56 @@
         <v>0.95</v>
       </c>
     </row>
+    <row r="116" spans="1:16" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="21">
+        <v>0</v>
+      </c>
+      <c r="E116" s="22">
+        <v>0</v>
+      </c>
+      <c r="F116" s="22">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>143.77000931573409</v>
+      </c>
+      <c r="I116" s="22">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="J116" s="22">
+        <v>98.404982600961887</v>
+      </c>
+      <c r="K116" s="21">
+        <v>242.17499191669597</v>
+      </c>
+      <c r="L116" s="26">
+        <v>44.283524022760979</v>
+      </c>
+      <c r="M116" s="27">
+        <v>64.40215697700657</v>
+      </c>
+      <c r="N116" s="27">
+        <v>73.812304204256705</v>
+      </c>
+      <c r="O116" s="27">
+        <v>45.581862522506299</v>
+      </c>
+      <c r="P116" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -60707,7 +61156,7 @@
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AH115"/>
+  <dimension ref="A1:AH116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -66112,6 +66561,47 @@
         <v>125.02031660046136</v>
       </c>
     </row>
+    <row r="116" spans="1:13" ht="12.75">
+      <c r="A116" s="15">
+        <v>46265</v>
+      </c>
+      <c r="B116" s="25">
+        <v>2.8069999217987061</v>
+      </c>
+      <c r="C116" s="20">
+        <v>1.3865164672617438</v>
+      </c>
+      <c r="D116" s="20">
+        <v>934559.9375</v>
+      </c>
+      <c r="E116" s="20">
+        <v>1822584.096999204</v>
+      </c>
+      <c r="F116" s="21">
+        <v>0</v>
+      </c>
+      <c r="G116" s="22">
+        <v>0</v>
+      </c>
+      <c r="H116" s="22">
+        <v>0</v>
+      </c>
+      <c r="I116" s="22">
+        <v>0</v>
+      </c>
+      <c r="J116" s="22">
+        <v>75.378225802571194</v>
+      </c>
+      <c r="K116" s="22">
+        <v>125.02031660046136</v>
+      </c>
+      <c r="L116" s="22">
+        <v>49.642090797890162</v>
+      </c>
+      <c r="M116" s="21">
+        <v>125.02031660046136</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="I3">
